--- a/data/VAT_Tax.xlsx
+++ b/data/VAT_Tax.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -582,6 +582,94 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>100002043</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Mooncake Label Lava Coffee (42 sticker/sheet)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Piece</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>08l</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>100002044</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Mooncake Label Matcha (42 sticker/sheet)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Piece</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>08l</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>100002045</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Mooncake Label Mixed Nut (42 sticker/sheet)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Piece</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>08l</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>100002042</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Mooncake Label Mungbean (42 sticker/sheet)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Piece</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>08l</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
